--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anin_mantenimiento.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anin_mantenimiento.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U77"/>
+  <dimension ref="A1:W77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,16 @@
       <c r="U1" t="inlineStr">
         <is>
           <t>ubigeo</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ugel</t>
         </is>
       </c>
     </row>
@@ -587,6 +597,16 @@
           <t>130401</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -648,6 +668,16 @@
           <t>130101</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>UGEL 03 - TRUJILLO NOR OESTE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -709,6 +739,16 @@
           <t>130705</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>UGEL PACASMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -770,6 +810,16 @@
           <t>130401</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -831,6 +881,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -892,6 +952,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -953,6 +1023,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1014,6 +1094,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1075,6 +1165,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1136,6 +1236,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1197,6 +1307,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1258,6 +1378,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1319,6 +1449,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1380,6 +1520,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1441,6 +1591,16 @@
           <t>140105</t>
         </is>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1502,6 +1662,16 @@
           <t>140105</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1563,6 +1733,16 @@
           <t>140105</t>
         </is>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1624,6 +1804,16 @@
           <t>140303</t>
         </is>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1685,6 +1875,16 @@
           <t>140105</t>
         </is>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1746,6 +1946,16 @@
           <t>240301</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1807,6 +2017,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1868,6 +2088,16 @@
           <t>021101</t>
         </is>
       </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1953,6 +2183,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2038,6 +2278,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2123,6 +2373,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2202,6 +2462,16 @@
       <c r="U27" t="inlineStr">
         <is>
           <t>021801</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
         </is>
       </c>
     </row>
@@ -2277,6 +2547,16 @@
           <t>020702</t>
         </is>
       </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>UGEL CARLOS FERMIN FITZCARRALD</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2350,6 +2630,16 @@
           <t>021203</t>
         </is>
       </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2423,6 +2713,16 @@
           <t>020110</t>
         </is>
       </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2504,6 +2804,16 @@
           <t>061007</t>
         </is>
       </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARCOS</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2583,6 +2893,16 @@
       <c r="U32" t="inlineStr">
         <is>
           <t>060203</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
         </is>
       </c>
     </row>
@@ -2646,6 +2966,16 @@
           <t>130207</t>
         </is>
       </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2727,6 +3057,16 @@
       <c r="U34" t="inlineStr">
         <is>
           <t>130208</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
         </is>
       </c>
     </row>
@@ -2790,6 +3130,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2855,6 +3205,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2920,6 +3280,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3005,6 +3375,16 @@
           <t>200507</t>
         </is>
       </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>UGEL PAITA</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3090,6 +3470,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3175,6 +3565,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3260,6 +3660,16 @@
           <t>200805</t>
         </is>
       </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3345,6 +3755,16 @@
           <t>200606</t>
         </is>
       </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3430,6 +3850,16 @@
           <t>200701</t>
         </is>
       </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3515,6 +3945,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3598,6 +4038,16 @@
       <c r="U45" t="inlineStr">
         <is>
           <t>200804</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
         </is>
       </c>
     </row>
@@ -3661,6 +4111,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3726,6 +4186,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3791,6 +4261,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3876,6 +4356,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3961,6 +4451,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4046,6 +4546,16 @@
       <c r="U51" t="inlineStr">
         <is>
           <t>022001</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
     </row>
@@ -4133,6 +4643,16 @@
           <t>090403</t>
         </is>
       </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>UGEL CASTROVIRREYNA</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4218,6 +4738,16 @@
           <t>150727</t>
         </is>
       </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4301,6 +4831,16 @@
       <c r="U54" t="inlineStr">
         <is>
           <t>150720</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
     </row>
@@ -4364,6 +4904,16 @@
           <t>130904</t>
         </is>
       </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4447,6 +4997,16 @@
       <c r="U56" t="inlineStr">
         <is>
           <t>130701</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>UGEL PACASMAYO</t>
         </is>
       </c>
     </row>
@@ -4510,6 +5070,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4571,6 +5141,16 @@
           <t>200703</t>
         </is>
       </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4632,6 +5212,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4717,6 +5307,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4802,6 +5402,16 @@
           <t>200109</t>
         </is>
       </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4887,6 +5497,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4972,6 +5592,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5057,6 +5687,16 @@
           <t>200603</t>
         </is>
       </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5140,6 +5780,16 @@
       <c r="U65" t="inlineStr">
         <is>
           <t>200114</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
     </row>
@@ -5203,6 +5853,16 @@
           <t>200107</t>
         </is>
       </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5264,6 +5924,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5347,6 +6017,16 @@
       <c r="U68" t="inlineStr">
         <is>
           <t>200701</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
         </is>
       </c>
     </row>
@@ -5410,6 +6090,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5471,6 +6161,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5532,6 +6232,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5593,6 +6303,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5654,6 +6374,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5715,6 +6445,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5776,6 +6516,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5837,6 +6587,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5898,6 +6658,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anin_mantenimiento.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anin_mantenimiento.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W77"/>
+  <dimension ref="A1:X77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,11 @@
       <c r="W1" t="inlineStr">
         <is>
           <t>ugel</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>fuente</t>
         </is>
       </c>
     </row>
@@ -607,6 +612,11 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -678,6 +688,11 @@
           <t>UGEL 03 - TRUJILLO NOR OESTE</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -749,6 +764,11 @@
           <t>UGEL PACASMAYO</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -820,6 +840,11 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -891,6 +916,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -962,6 +992,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1033,6 +1068,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1104,6 +1144,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1175,6 +1220,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1246,6 +1296,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1317,6 +1372,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1388,6 +1448,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1459,6 +1524,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1530,6 +1600,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1601,6 +1676,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1672,6 +1752,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1743,6 +1828,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1814,6 +1904,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1885,6 +1980,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1956,6 +2056,11 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2027,6 +2132,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2098,6 +2208,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2193,6 +2308,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2288,6 +2408,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2383,6 +2508,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2472,6 +2602,11 @@
       <c r="W27" t="inlineStr">
         <is>
           <t>UGEL SANTA</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>ANIN</t>
         </is>
       </c>
     </row>
@@ -2557,6 +2692,11 @@
           <t>UGEL CARLOS FERMIN FITZCARRALD</t>
         </is>
       </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2640,6 +2780,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2723,6 +2868,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2814,6 +2964,11 @@
           <t>UGEL SAN MARCOS</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2903,6 +3058,11 @@
       <c r="W32" t="inlineStr">
         <is>
           <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>ANIN</t>
         </is>
       </c>
     </row>
@@ -2976,6 +3136,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3067,6 +3232,11 @@
       <c r="W34" t="inlineStr">
         <is>
           <t>UGEL ASCOPE</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>ANIN</t>
         </is>
       </c>
     </row>
@@ -3140,6 +3310,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3215,6 +3390,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3290,6 +3470,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3385,6 +3570,11 @@
           <t>UGEL PAITA</t>
         </is>
       </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3480,6 +3670,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3575,6 +3770,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3670,6 +3870,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3765,6 +3970,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3860,6 +4070,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3955,6 +4170,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4048,6 +4268,11 @@
       <c r="W45" t="inlineStr">
         <is>
           <t>UGEL SECHURA</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>ANIN</t>
         </is>
       </c>
     </row>
@@ -4121,6 +4346,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4196,6 +4426,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4271,6 +4506,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4366,6 +4606,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4461,6 +4706,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4556,6 +4806,11 @@
       <c r="W51" t="inlineStr">
         <is>
           <t>UGEL YUNGAY</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>ANIN</t>
         </is>
       </c>
     </row>
@@ -4653,6 +4908,11 @@
           <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4748,6 +5008,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4841,6 +5106,11 @@
       <c r="W54" t="inlineStr">
         <is>
           <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>ANIN</t>
         </is>
       </c>
     </row>
@@ -4914,6 +5184,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5007,6 +5282,11 @@
       <c r="W56" t="inlineStr">
         <is>
           <t>UGEL PACASMAYO</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>ANIN</t>
         </is>
       </c>
     </row>
@@ -5080,6 +5360,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5151,6 +5436,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5222,6 +5512,11 @@
           <t>DRE TUMBES</t>
         </is>
       </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5317,6 +5612,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5412,6 +5712,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5507,6 +5812,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5602,6 +5912,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5697,6 +6012,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5790,6 +6110,11 @@
       <c r="W65" t="inlineStr">
         <is>
           <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>ANIN</t>
         </is>
       </c>
     </row>
@@ -5863,6 +6188,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5934,6 +6264,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6027,6 +6362,11 @@
       <c r="W68" t="inlineStr">
         <is>
           <t>UGEL TALARA</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>ANIN</t>
         </is>
       </c>
     </row>
@@ -6100,6 +6440,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6171,6 +6516,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6242,6 +6592,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6313,6 +6668,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6384,6 +6744,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6455,6 +6820,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6526,6 +6896,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6597,6 +6972,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6668,6 +7048,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>ANIN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anin_mantenimiento.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anin_mantenimiento.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X77"/>
+  <dimension ref="A1:Z77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,16 @@
         </is>
       </c>
       <c r="X1" t="inlineStr">
+        <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -614,6 +624,16 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>80830 ZOILA HORA DE ROBLES/1639/80830 ZOILA HORA DE ROBLES</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -690,6 +710,16 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>80892 LOS PINOS/80892 LOS PINOS</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -766,6 +796,16 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>80669/80669</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -842,6 +882,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>CARLOS A. OLIVARES/80382 CARLOS A. OLIVARES/80382 CARLOS A. OLIVARES</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -918,6 +968,16 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>88014 JOSE OLAYA/88014 JOSE OLAYA/88014 JOSE OLAYA</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -994,6 +1054,16 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
+          <t>88104 MARIA PARADO DE BELLIDO/88104 MARIA PARADO DE BELLIDO/88104 MARIA PARADO DE BELLIDO</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1070,6 +1140,16 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
+          <t>1556 ANGELITOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1146,6 +1226,16 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>88232 NUESTRA VIRGEN MARIA/88232 NUESTRA VIRGEN MARIA</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1222,6 +1312,16 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
+          <t>88331/88331</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1298,6 +1398,16 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
+          <t>89008 ANDRES AVELINO CACERES/89008 ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1374,6 +1484,16 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
+          <t>88227 PEDRO PABLO ATUSPARIA/88227 PEDRO PABLO ATUSPARIA/88227 PEDRO PABLO ATUSPARIA</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1450,6 +1570,16 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
+          <t>88100 INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1526,6 +1656,16 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
+          <t>88037 ANTENOR SANCHEZ/88037 ANTENOR SANCHEZ/88037 ANTENOR SANCHEZ</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1602,6 +1742,16 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
+          <t>88034 PEDRO RUIZ GALLO/88034 PEDRO RUIZ GALLO</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1678,6 +1828,16 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
+          <t>11057 SAN LORENZO/11057 SAN LORENZO/11057 SAN LORENZO</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1754,6 +1914,16 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
+          <t>11011 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1830,6 +2000,16 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
+          <t>MARIANO MELGAR VALDIVIEZO</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1906,6 +2086,16 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
+          <t>SAN JUAN/SAN JUAN/SAN JUAN</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -1982,6 +2172,16 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
+          <t>10945 HEROINA MARIA PARADO DE BELLIDO</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -2058,6 +2258,16 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
+          <t>094 SOTERITO LOPEZ ESPINOZA</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -2134,6 +2344,16 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
+          <t>005 TARCILLA DE JESUS GRANDA MORA</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -2210,6 +2430,16 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
+          <t>88106 JOSE CARLOS MARIATEGUI/88106 JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -2310,6 +2540,16 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
+          <t>88336 GASTON VIDAL PORTURAS/88336 GASTON VIDAL PORTURAS</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -2410,6 +2650,16 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
+          <t>88301/88301</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -2510,6 +2760,16 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
+          <t>89001/89001</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -2605,6 +2865,16 @@
         </is>
       </c>
       <c r="X27" t="inlineStr">
+        <is>
+          <t>88023 ALMIRANTE MIGUEL GRAU SEMINARIO/88023 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2694,6 +2964,16 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
+          <t>84156/84156</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -2782,6 +3062,16 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
+          <t>86499 LUIS TORRES SALAZAR/86499 LUIS TORRES SALAZAR</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -2870,6 +3160,16 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
+          <t>86127/86127/86127</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -2966,6 +3266,16 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
+          <t>821356</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -3061,6 +3371,16 @@
         </is>
       </c>
       <c r="X32" t="inlineStr">
+        <is>
+          <t>82323/82323</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3138,6 +3458,16 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
+          <t>81534 IRIS BARRIGA GALARRETA</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -3235,6 +3565,16 @@
         </is>
       </c>
       <c r="X34" t="inlineStr">
+        <is>
+          <t>CASA GRANDE/CASA GRANDE/CASA GRANDE</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3312,6 +3652,16 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
+          <t>14037 SANTIAGO A REQUENA CASTRO/14037 SANTIAGO A REQUENA CASTRO</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -3392,6 +3742,16 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
+          <t>14065/14065</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -3472,6 +3832,16 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
+          <t>MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -3572,6 +3942,16 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
+          <t>RICARDO PALMA</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -3672,6 +4052,16 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
+          <t>VIRGEN DEL CARMEN/VIRGEN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -3772,6 +4162,16 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
+          <t>14654</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -3872,6 +4272,16 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
+          <t>14010 MIGUEL F. CERRO</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -3972,6 +4382,16 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
+          <t>14858</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -4072,6 +4492,16 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
+          <t>IGNACIO MERINO/IGNACIO MERINO</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -4172,6 +4602,16 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
+          <t>14062 NUESTRA SEÑORA DE LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -4271,6 +4711,16 @@
         </is>
       </c>
       <c r="X45" t="inlineStr">
+        <is>
+          <t>SAN CRISTO/SAN CRISTO/SAN CRISTO</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4348,6 +4798,16 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
+          <t>1563 CRISTO REY AMIGO DE LOS NIÑOS</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -4428,6 +4888,16 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
+          <t>88229 SAN JUAN/88229 SAN JUAN</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -4508,6 +4978,16 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
+          <t>VILLA MARIA/VILLA MARIA/VILLA MARIA</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -4608,6 +5088,16 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
+          <t>88032 APOSTOL SAN PEDRO/88032 APOSTOL SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -4708,6 +5198,16 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
+          <t>86625 ANGELICA HARADA VASQUEZ/86625 ANGELICA HARADA VASQUEZ</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -4809,6 +5309,16 @@
         </is>
       </c>
       <c r="X51" t="inlineStr">
+        <is>
+          <t>86620 SANTA FE/86620 SANTA FE</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4910,6 +5420,16 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
+          <t>ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -5010,6 +5530,16 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
+          <t>20811 REPUBLICA DE COLOMBIA/20811 REPUBLICA DE COLOMBIA/20811 REPUBLICA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -5109,6 +5639,16 @@
         </is>
       </c>
       <c r="X54" t="inlineStr">
+        <is>
+          <t>20653 SAN JUAN BAUTISTA PRECURSOR/20653 SAN JUAN BAUTISTA PRECURSOR/20653 SAN JUAN BAUTISTA PRECURSOR</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5186,6 +5726,16 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
+          <t>80138 ABELARDO GAMARRA RONDO/80138 ABELARDO GAMARRA RONDO</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -5285,6 +5835,16 @@
         </is>
       </c>
       <c r="X56" t="inlineStr">
+        <is>
+          <t>80374 JOSE SEVILLA ESCAJADILLO</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5362,6 +5922,16 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
+          <t>JOSE MATIAS MANZANILLA</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -5438,6 +6008,16 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
+          <t>LA BREA</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -5514,6 +6094,16 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
+          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -5614,6 +6204,16 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
+          <t>14594 SAN JOSE/14594 SAN JOSE/14594 SAN JOSE</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -5714,6 +6314,16 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
+          <t>COLEGIO TECNICO DE APLICACION/COLEGIO TECNICO DE APLICACION</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -5814,6 +6424,16 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
+          <t>14641</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -5914,6 +6534,16 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
+          <t>14790 MARIA IGNACIA GARCIA DE GONZALES/14790 MARIA IGNACIA GARCIA</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6014,6 +6644,16 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
+          <t>20509/20509</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6113,6 +6753,16 @@
         </is>
       </c>
       <c r="X65" t="inlineStr">
+        <is>
+          <t>14924 DANIEL ALCIDES CARRION/14924 DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6190,6 +6840,16 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
+          <t>CORONEL JOSE ANDRES RAZURI/CORONEL JOSE ANDRES RAZURI/CORONEL JOSE ANDRES RAZURI</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6266,6 +6926,16 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
+          <t>15079/15079/15079</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6365,6 +7035,16 @@
         </is>
       </c>
       <c r="X68" t="inlineStr">
+        <is>
+          <t>15508 DOMINGO SAVIO/15508 DOMINGO SAVIO/15508 DOMINGO SAVIO</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6442,6 +7122,16 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
+          <t>GENARO MARTINEZ SILVA/GENARO MARTINEZ SILVA/GENARO MARTINEZ SILVA</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6518,6 +7208,16 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
+          <t>JOSE JACOBO CRUZ VILLEGAS/JOSE JACOBO CRUZ VILLEGAS</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6594,6 +7294,16 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
+          <t>JOSE CAYETANO HEREDIA</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6670,6 +7380,16 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
+          <t>15027 AMAUTA/15027 AMAUTA/15027 AMAUTA</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6746,6 +7466,16 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6822,6 +7552,16 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
+          <t>14064</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6898,6 +7638,16 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
+          <t>MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -6974,6 +7724,16 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
+          <t>86756</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>
@@ -7050,6 +7810,16 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
+          <t>86657 JUAN CLAROS VERAZ/86657 JUAN CLAROS VERAZ/86657 JUAN CLAROS VERAZ</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
           <t>ANIN</t>
         </is>
       </c>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anin_mantenimiento.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anin_mantenimiento.xlsx
@@ -423,82 +423,82 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CUI (IRI)</t>
+          <t>cui</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Código Local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Nombre del IRI</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>- Activo intervenido (equipamiento educativo, mobiliario, instalaciones sanitarias, instalaciones eléctricas y mecánicas, tecnologías de la información y comunicaciones, sistemas de detección y alarmas, coberturas, acabados y exteriores).</t>
+          <t>activo_intervenido_equipamiento_educativo_mobiliario_instala</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Tipo de mantenimiento a ejecutar, de acuerdo con la OTM (Orden de Trabajo de Mantenimiento). Las categorías son: Mantenimiento recurrente, Mantenimiento preventivo, Mantenimienro correctivo.</t>
+          <t>tipo_de_mantenimiento_a_ejecutar_de_acuerdo_con_la_otm_orden</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Monto de la intervención total</t>
+          <t>monto_de_la_intervencion_total</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Monto de la intervención 2025</t>
+          <t>monto_de_la_intervencion_2025</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Monto de la intervención 2026</t>
+          <t>monto_de_la_intervencion_2026</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Monto de la intervención 2027</t>
+          <t>monto_de_la_intervencion_2027</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Monto de la intervención 2028</t>
+          <t>monto_de_la_intervencion_2028</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Avance (%)</t>
+          <t>avance</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Año de la entrega de la IRI</t>
+          <t>ano_de_la_entrega_de_la_iri</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Fecha de inicio (o estimada)</t>
+          <t>fecha_inicio</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Fecha de culminación (o estimada)</t>
+          <t>fecha_culminacion</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Comentarios (- Otras variables que se consideren pertinentes para el seguimiento del avance en el cierre de brechas.)</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anin_mantenimiento.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anin_mantenimiento.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z77"/>
+  <dimension ref="A1:X77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,80 +473,70 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>monto_de_la_intervencion_2028</t>
+          <t>ano_de_la_entrega_de_la_iri</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>avance</t>
+          <t>fecha_inicio</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>ano_de_la_entrega_de_la_iri</t>
+          <t>fecha_culminacion</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>fecha_inicio</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>fecha_culminacion</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>centro_poblado</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>ubigeo</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>centro_poblado</t>
+          <t>dre</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>ubigeo</t>
+          <t>ugel</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>dre</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>ugel</t>
+          <t>area</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
-        <is>
-          <t>nombre_ie_2</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -580,16 +570,24 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>CHEPEN</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>CHEPEN</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -599,40 +597,30 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CHEPEN</t>
+          <t>130401</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CHEPEN</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>130401</t>
+          <t>UGEL CHEPEN</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>GRE LA LIBERTAD</t>
+          <t>80830 ZOILA HORA DE ROBLES/1639/80830 ZOILA HORA DE ROBLES</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>UGEL CHEPEN</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
-        <is>
-          <t>80830 ZOILA HORA DE ROBLES/1639/80830 ZOILA HORA DE ROBLES</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -666,16 +654,24 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -685,40 +681,30 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>130101</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>130101</t>
+          <t>UGEL 03 - TRUJILLO NOR OESTE</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>GRE LA LIBERTAD</t>
+          <t>80892 LOS PINOS/80892 LOS PINOS</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>UGEL 03 - TRUJILLO NOR OESTE</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
-        <is>
-          <t>80892 LOS PINOS/80892 LOS PINOS</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -752,59 +738,57 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>PACASMAYO</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>SAN JOSE</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>PACASMAYO</t>
+          <t>PORTADA DE LA SIERRA</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>SAN JOSE</t>
+          <t>130705</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>PORTADA DE LA SIERRA</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>130705</t>
+          <t>UGEL PACASMAYO</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>GRE LA LIBERTAD</t>
+          <t>80669/80669</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>UGEL PACASMAYO</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
-        <is>
-          <t>80669/80669</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -838,16 +822,24 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>CHEPEN</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>CHEPEN</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -857,40 +849,30 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CHEPEN</t>
+          <t>130401</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>CHEPEN</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>130401</t>
+          <t>UGEL CHEPEN</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>GRE LA LIBERTAD</t>
+          <t>CARLOS A. OLIVARES/80382 CARLOS A. OLIVARES/80382 CARLOS A. OLIVARES</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>UGEL CHEPEN</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
-        <is>
-          <t>CARLOS A. OLIVARES/80382 CARLOS A. OLIVARES/80382 CARLOS A. OLIVARES</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -924,59 +906,57 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>MIRAFLORES ALTO</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>021801</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>MIRAFLORES ALTO</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88014 JOSE OLAYA/88014 JOSE OLAYA/88014 JOSE OLAYA</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
-        <is>
-          <t>88014 JOSE OLAYA/88014 JOSE OLAYA/88014 JOSE OLAYA</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1010,59 +990,57 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>CASMA</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CASMA</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>CASMA</t>
+          <t>NIVIN</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CASMA</t>
+          <t>020801</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>NIVIN</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>020801</t>
+          <t>UGEL CASMA</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88104 MARIA PARADO DE BELLIDO/88104 MARIA PARADO DE BELLIDO/88104 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>UGEL CASMA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
-        <is>
-          <t>88104 MARIA PARADO DE BELLIDO/88104 MARIA PARADO DE BELLIDO/88104 MARIA PARADO DE BELLIDO</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1096,59 +1074,57 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>CASMA</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CASMA</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>CASMA</t>
+          <t>EL PALMO</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CASMA</t>
+          <t>020801</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>EL PALMO</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>020801</t>
+          <t>UGEL CASMA</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>1556 ANGELITOS DE JESUS</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>UGEL CASMA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
-        <is>
-          <t>1556 ANGELITOS DE JESUS</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1182,59 +1158,57 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>021801</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88232 NUESTRA VIRGEN MARIA/88232 NUESTRA VIRGEN MARIA</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
-        <is>
-          <t>88232 NUESTRA VIRGEN MARIA/88232 NUESTRA VIRGEN MARIA</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1268,59 +1242,57 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>RINCONADA</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>021801</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>RINCONADA</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88331/88331</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
-        <is>
-          <t>88331/88331</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1354,59 +1326,57 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>ESPERANZA BAJA</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>021801</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>ESPERANZA BAJA</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>89008 ANDRES AVELINO CACERES/89008 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
-        <is>
-          <t>89008 ANDRES AVELINO CACERES/89008 ANDRES AVELINO CACERES</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1440,59 +1410,57 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>LOS HEROES</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>021809</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>LOS HEROES</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>021809</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88227 PEDRO PABLO ATUSPARIA/88227 PEDRO PABLO ATUSPARIA/88227 PEDRO PABLO ATUSPARIA</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
-        <is>
-          <t>88227 PEDRO PABLO ATUSPARIA/88227 PEDRO PABLO ATUSPARIA/88227 PEDRO PABLO ATUSPARIA</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1526,16 +1494,24 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>CASMA</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CASMA</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1545,40 +1521,30 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CASMA</t>
+          <t>020801</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>CASMA</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>020801</t>
+          <t>UGEL CASMA</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88100 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>UGEL CASMA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
-        <is>
-          <t>88100 INMACULADA CONCEPCION</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1612,59 +1578,57 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>021801</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>LA UNION</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88037 ANTENOR SANCHEZ/88037 ANTENOR SANCHEZ/88037 ANTENOR SANCHEZ</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
-        <is>
-          <t>88037 ANTENOR SANCHEZ/88037 ANTENOR SANCHEZ/88037 ANTENOR SANCHEZ</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1698,59 +1662,57 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>2 DE JUNIO</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>021801</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2 DE JUNIO</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88034 PEDRO RUIZ GALLO/88034 PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
-        <is>
-          <t>88034 PEDRO RUIZ GALLO/88034 PEDRO RUIZ GALLO</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1784,59 +1746,57 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>CHICLAYO</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>JOSE LEONARDO ORTIZ</t>
+          <t>140105</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>JOSE LEONARDO ORTIZ</t>
+          <t>GRE LAMBAYEQUE</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>140105</t>
+          <t>UGEL CHICLAYO</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>GRE LAMBAYEQUE</t>
+          <t>11057 SAN LORENZO/11057 SAN LORENZO/11057 SAN LORENZO</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>UGEL CHICLAYO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
-        <is>
-          <t>11057 SAN LORENZO/11057 SAN LORENZO/11057 SAN LORENZO</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1870,59 +1830,57 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>CHICLAYO</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>JOSE LEONARDO ORTIZ</t>
+          <t>140105</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>JOSE LEONARDO ORTIZ</t>
+          <t>GRE LAMBAYEQUE</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>140105</t>
+          <t>UGEL CHICLAYO</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>GRE LAMBAYEQUE</t>
+          <t>11011 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>UGEL CHICLAYO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
-        <is>
-          <t>11011 SEÑOR DE LOS MILAGROS</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -1956,59 +1914,57 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>CHICLAYO</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>JOSE LEONARDO ORTIZ</t>
+          <t>140105</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>JOSE LEONARDO ORTIZ</t>
+          <t>GRE LAMBAYEQUE</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>140105</t>
+          <t>UGEL CHICLAYO</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>GRE LAMBAYEQUE</t>
+          <t>MARIANO MELGAR VALDIVIEZO</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>UGEL CHICLAYO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
-        <is>
-          <t>MARIANO MELGAR VALDIVIEZO</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2042,59 +1998,57 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>LAMBAYEQUE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>ILLIMO</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>ILLIMO</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>ILLIMO</t>
+          <t>140303</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>ILLIMO</t>
+          <t>GRE LAMBAYEQUE</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>140303</t>
+          <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>GRE LAMBAYEQUE</t>
+          <t>SAN JUAN/SAN JUAN/SAN JUAN</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>UGEL LAMBAYEQUE</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
-        <is>
-          <t>SAN JUAN/SAN JUAN/SAN JUAN</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2128,59 +2082,57 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>CHICLAYO</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>JOSE LEONARDO ORTIZ</t>
+          <t>140105</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>JOSE LEONARDO ORTIZ</t>
+          <t>GRE LAMBAYEQUE</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>140105</t>
+          <t>UGEL CHICLAYO</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>GRE LAMBAYEQUE</t>
+          <t>10945 HEROINA MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>UGEL CHICLAYO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
-        <is>
-          <t>10945 HEROINA MARIA PARADO DE BELLIDO</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2214,16 +2166,24 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>ZARUMILLA</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>TUMBES</t>
+          <t>ZARUMILLA</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2233,40 +2193,30 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>ZARUMILLA</t>
+          <t>240301</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>ZARUMILLA</t>
+          <t>DRE TUMBES</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>240301</t>
+          <t>UGEL ZARUMILLA</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>DRE TUMBES</t>
+          <t>094 SOTERITO LOPEZ ESPINOZA</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>UGEL ZARUMILLA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
-        <is>
-          <t>094 SOTERITO LOPEZ ESPINOZA</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2300,11 +2250,19 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>TUMBES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2314,45 +2272,35 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>TUMBES</t>
+          <t>EL MILAGRO</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>TUMBES</t>
+          <t>240101</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>EL MILAGRO</t>
+          <t>DRE TUMBES</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>240101</t>
+          <t>UGEL TUMBES</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>DRE TUMBES</t>
+          <t>005 TARCILLA DE JESUS GRANDA MORA</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>UGEL TUMBES</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
-        <is>
-          <t>005 TARCILLA DE JESUS GRANDA MORA</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2386,16 +2334,24 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>HUARMEY</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>HUARMEY</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2405,40 +2361,30 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>HUARMEY</t>
+          <t>021101</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>HUARMEY</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>021101</t>
+          <t>UGEL HUARMEY</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88106 JOSE CARLOS MARIATEGUI/88106 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>UGEL HUARMEY</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
-        <is>
-          <t>88106 JOSE CARLOS MARIATEGUI/88106 JOSE CARLOS MARIATEGUI</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2483,72 +2429,70 @@
         <v>134500</v>
       </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" s="1" t="n">
+      <c r="K24" s="1" t="n">
         <v>45355</v>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>27/11/2024</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>26/11/2028</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>26/11/2028</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>EL DORADO</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>021809</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>EL DORADO</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>021809</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88336 GASTON VIDAL PORTURAS/88336 GASTON VIDAL PORTURAS</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
-        <is>
-          <t>88336 GASTON VIDAL PORTURAS/88336 GASTON VIDAL PORTURAS</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2593,72 +2537,70 @@
         <v>265200</v>
       </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" s="1" t="n">
+      <c r="K25" s="1" t="n">
         <v>45630</v>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>24/02/2025</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>23/02/2029</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>23/02/2029</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>HUAYLAS</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>PAMPAROMAS</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>HUAYLAS</t>
+          <t>PISHIA</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>PAMPAROMAS</t>
+          <t>021206</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>PISHIA</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>021206</t>
+          <t>UGEL HUAYLAS</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88301/88301</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>UGEL HUAYLAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
-        <is>
-          <t>88301/88301</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2703,72 +2645,70 @@
         <v>138600.34</v>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" s="1" t="n">
+      <c r="K26" s="1" t="n">
         <v>45705</v>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>17/02/2025</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>16/02/2029</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>17/02/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>16/02/2029</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>021801</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>89001/89001</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
-        <is>
-          <t>89001/89001</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2809,72 +2749,70 @@
         <v>156800</v>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" s="1" t="n">
+      <c r="K27" s="1" t="n">
         <v>45723</v>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>26/08/2029</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>27/08/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>26/08/2029</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>EL ACERO</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>021801</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>EL ACERO</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88023 ALMIRANTE MIGUEL GRAU SEMINARIO/88023 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
-        <is>
-          <t>88023 ALMIRANTE MIGUEL GRAU SEMINARIO/88023 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -2910,69 +2848,67 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>31/08/2030</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>Institución educativa en proceso de ejecución de obra.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Institución educativa en proceso de ejecución de obra.</t>
+          <t>CARLOS FERMIN FITZCARRALD</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>SAN NICOLAS</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>CARLOS FERMIN FITZCARRALD</t>
+          <t>RANCHAJ</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>SAN NICOLAS</t>
+          <t>020702</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>RANCHAJ</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>020702</t>
+          <t>UGEL CARLOS FERMIN FITZCARRALD</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>84156/84156</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>UGEL CARLOS FERMIN FITZCARRALD</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
-        <is>
-          <t>84156/84156</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3008,69 +2944,67 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>31/08/2030</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>Institución educativa en proceso de ejecución de obra.</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Institución educativa en proceso de ejecución de obra.</t>
+          <t>HUAYLAS</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>HUATA</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>HUAYLAS</t>
+          <t>HUATA</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>HUATA</t>
+          <t>021203</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>HUATA</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>021203</t>
+          <t>UGEL HUAYLAS</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>86499 LUIS TORRES SALAZAR/86499 LUIS TORRES SALAZAR</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>UGEL HUAYLAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
-        <is>
-          <t>86499 LUIS TORRES SALAZAR/86499 LUIS TORRES SALAZAR</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3106,69 +3040,67 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>31/08/2030</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>Institución educativa en proceso de ejecución de obra.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Institución educativa en proceso de ejecución de obra.</t>
+          <t>HUARAZ</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>PARIACOTO</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>HUARAZ</t>
+          <t>CACCHAN</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>PARIACOTO</t>
+          <t>020110</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>CACCHAN</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>020110</t>
+          <t>UGEL HUARAZ</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>86127/86127/86127</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>UGEL HUARAZ</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
-        <is>
-          <t>86127/86127/86127</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3213,68 +3145,66 @@
         <v>189146.34</v>
       </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" s="1" t="n">
+      <c r="K31" s="1" t="n">
         <v>45356</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>21/02/2025</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>20/02/2029</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>20/02/2029</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SAN MARCOS</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>JOSE SABOGAL</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>PAMPA ALEGRE</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>JOSE SABOGAL</t>
+          <t>061007</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>PAMPA ALEGRE</t>
+          <t>DRE CAJAMARCA</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>061007</t>
+          <t>UGEL SAN MARCOS</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>DRE CAJAMARCA</t>
+          <t>821356</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>UGEL SAN MARCOS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
-        <is>
-          <t>821356</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3319,68 +3249,66 @@
         <v>196969.89</v>
       </c>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" s="1" t="n">
+      <c r="K32" s="1" t="n">
         <v>45720</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>12/05/2025</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>11/05/2029</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>11/05/2029</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>CAJABAMBA</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>CONDEBAMBA</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>CAJABAMBA</t>
+          <t>TANGALBAMBA</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>CONDEBAMBA</t>
+          <t>060203</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>TANGALBAMBA</t>
+          <t>DRE CAJAMARCA</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>060203</t>
+          <t>UGEL CAJABAMBA</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>DRE CAJAMARCA</t>
+          <t>82323/82323</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>UGEL CAJABAMBA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
-        <is>
-          <t>82323/82323</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3414,59 +3342,57 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>ASCOPE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>SANTIAGO DE CAO</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>ASCOPE</t>
+          <t>CHIQUITOY</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>SANTIAGO DE CAO</t>
+          <t>130207</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>CHIQUITOY</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>130207</t>
+          <t>UGEL ASCOPE</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>GRE LA LIBERTAD</t>
+          <t>81534 IRIS BARRIGA GALARRETA</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>UGEL ASCOPE</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
-        <is>
-          <t>81534 IRIS BARRIGA GALARRETA</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3509,72 +3435,70 @@
         <v>209084.14</v>
       </c>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" s="1" t="n">
+      <c r="K34" s="1" t="n">
         <v>45530</v>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>10/01/2025</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>09/01/2029</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>09/01/2029</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>ASCOPE</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>CASA GRANDE</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>ASCOPE</t>
+          <t>CASA GRANDE</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>CASA GRANDE</t>
+          <t>130208</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>CASA GRANDE</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>130208</t>
+          <t>UGEL ASCOPE</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>GRE LA LIBERTAD</t>
+          <t>CASA GRANDE/CASA GRANDE/CASA GRANDE</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>UGEL ASCOPE</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
-        <is>
-          <t>CASA GRANDE/CASA GRANDE/CASA GRANDE</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3608,59 +3532,57 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>200105</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>200105</t>
+          <t>UGEL PIURA</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14037 SANTIAGO A REQUENA CASTRO/14037 SANTIAGO A REQUENA CASTRO</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>UGEL PIURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
-        <is>
-          <t>14037 SANTIAGO A REQUENA CASTRO/14037 SANTIAGO A REQUENA CASTRO</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3693,64 +3615,62 @@
         <v>100000</v>
       </c>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" s="1" t="n">
+        <v>45288</v>
+      </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>En proceso de suscripción de convenio, para delegación de facultades de mantenimiento a la ANIN.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>En proceso de suscripción de convenio, para delegación de facultades de mantenimiento a la ANIN.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>YAPATO</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>LA UNION</t>
+          <t>200110</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>YAPATO</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>200110</t>
+          <t>UGEL LA UNIÓN</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14065/14065</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>UGEL LA UNIÓN</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
-        <is>
-          <t>14065/14065</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3783,64 +3703,62 @@
         <v>120000</v>
       </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" s="1" t="n">
+        <v>45281</v>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>En proceso de suscripción de convenio, para delegación de facultades de mantenimiento a la ANIN.</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>En proceso de suscripción de convenio, para delegación de facultades de mantenimiento a la ANIN.</t>
+          <t>MORROPON</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CHULUCANAS</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>MORROPON</t>
+          <t>CHULUCANAS</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>CHULUCANAS</t>
+          <t>200401</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>CHULUCANAS</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>200401</t>
+          <t>UGEL CHULUCANAS</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>UGEL CHULUCANAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
-        <is>
-          <t>MARIA AUXILIADORA</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3885,72 +3803,70 @@
         <v>152215.55</v>
       </c>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" s="1" t="n">
+      <c r="K38" s="1" t="n">
         <v>45348</v>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>PAITA</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>VICHAYAL</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>PAITA</t>
+          <t>MIRAMAR</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>VICHAYAL</t>
+          <t>200507</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>MIRAMAR</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>200507</t>
+          <t>UGEL PAITA</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>UGEL PAITA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
-        <is>
-          <t>RICARDO PALMA</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -3995,72 +3911,70 @@
         <v>166635.89</v>
       </c>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" s="1" t="n">
+      <c r="K39" s="1" t="n">
         <v>45405</v>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>200105</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>200105</t>
+          <t>UGEL PIURA</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>VIRGEN DEL CARMEN/VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>UGEL PIURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
-        <is>
-          <t>VIRGEN DEL CARMEN/VIRGEN DEL CARMEN</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4105,72 +4019,70 @@
         <v>164439.07</v>
       </c>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" s="1" t="n">
+      <c r="K40" s="1" t="n">
         <v>45461</v>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>MORROPON</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>SALITRAL</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>MORROPON</t>
+          <t>SALITRAL</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>SALITRAL</t>
+          <t>200406</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>SALITRAL</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>200406</t>
+          <t>UGEL MORROPÓN</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>UGEL MORROPÓN</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
-        <is>
-          <t>14654</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4215,72 +4127,70 @@
         <v>141507.55</v>
       </c>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" s="1" t="n">
+      <c r="K41" s="1" t="n">
         <v>45468</v>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>SECHURA</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>VICE</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>SECHURA</t>
+          <t>VICE</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>VICE</t>
+          <t>200805</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>VICE</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>200805</t>
+          <t>UGEL SECHURA</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14010 MIGUEL F. CERRO</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>UGEL SECHURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
-        <is>
-          <t>14010 MIGUEL F. CERRO</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4325,72 +4235,70 @@
         <v>135335.1</v>
       </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" s="1" t="n">
+      <c r="K42" s="1" t="n">
         <v>45495</v>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>MIGUEL CHECA</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>JIBITO</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>MIGUEL CHECA</t>
+          <t>200606</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>JIBITO</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>200606</t>
+          <t>UGEL SULLANA</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>UGEL SULLANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
-        <is>
-          <t>14858</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4435,29 +4343,37 @@
         <v>153926</v>
       </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" s="1" t="n">
+      <c r="K43" s="1" t="n">
         <v>45631</v>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>23/04/2025</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>22/04/2029</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>22/04/2029</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>TALARA</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>PARIÑAS</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4467,40 +4383,30 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>PARIÑAS</t>
+          <t>200701</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>TALARA</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>200701</t>
+          <t>UGEL TALARA</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>IGNACIO MERINO/IGNACIO MERINO</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>UGEL TALARA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
-        <is>
-          <t>IGNACIO MERINO/IGNACIO MERINO</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4545,72 +4451,70 @@
         <v>111091.53</v>
       </c>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" s="1" t="n">
+      <c r="K44" s="1" t="n">
         <v>45653</v>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>23/04/2025</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>22/04/2029</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>22/04/2029</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>TABLAZO NORTE</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>LA UNION</t>
+          <t>200110</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>TABLAZO NORTE</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>200110</t>
+          <t>UGEL LA UNIÓN</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14062 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>UGEL LA UNIÓN</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
-        <is>
-          <t>14062 NUESTRA SEÑORA DE LAS MERCEDES</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4655,72 +4559,70 @@
         <v>128900</v>
       </c>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" s="1" t="n">
+      <c r="K45" s="1" t="n">
         <v>45891</v>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>15/05/2025</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>14/05/2029</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>14/05/2029</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>SECHURA</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CRISTO NOS VALGA</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>SECHURA</t>
+          <t>SAN CRISTO</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>CRISTO NOS VALGA</t>
+          <t>200804</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>SAN CRISTO</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>200804</t>
+          <t>UGEL SECHURA</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>SAN CRISTO/SAN CRISTO/SAN CRISTO</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>UGEL SECHURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
-        <is>
-          <t>SAN CRISTO/SAN CRISTO/SAN CRISTO</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4754,59 +4656,57 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>021809</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>021809</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>1563 CRISTO REY AMIGO DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
-        <is>
-          <t>1563 CRISTO REY AMIGO DE LOS NIÑOS</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4839,64 +4739,62 @@
         <v>100000</v>
       </c>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" s="1" t="n">
+        <v>45281</v>
+      </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>En proceso de suscripción de convenio, para delegación de facultades de mantenimiento a la ANIN.</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>En proceso de suscripción de convenio, para delegación de facultades de mantenimiento a la ANIN.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>MIRAFLORES ALTO</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>021801</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>MIRAFLORES ALTO</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88229 SAN JUAN/88229 SAN JUAN</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
-        <is>
-          <t>88229 SAN JUAN/88229 SAN JUAN</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -4929,64 +4827,62 @@
         <v>100000</v>
       </c>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" s="1" t="n">
+        <v>45289</v>
+      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="1" t="n">
-        <v>45289</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>En proceso de suscripción de convenio, para delegación de facultades de mantenimiento a la ANIN.</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>En proceso de suscripción de convenio, para delegación de facultades de mantenimiento a la ANIN.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>VILLA MARIA</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>021809</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>VILLA MARIA</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>021809</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>VILLA MARIA/VILLA MARIA/VILLA MARIA</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
-        <is>
-          <t>VILLA MARIA/VILLA MARIA/VILLA MARIA</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5031,72 +4927,70 @@
         <v>155800.06</v>
       </c>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" s="1" t="n">
+      <c r="K49" s="1" t="n">
         <v>45576</v>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>27/11/2024</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>26/11/2028</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>26/11/2028</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>021801</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>021801</t>
+          <t>UGEL SANTA</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>88032 APOSTOL SAN PEDRO/88032 APOSTOL SAN PEDRO</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>UGEL SANTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
-        <is>
-          <t>88032 APOSTOL SAN PEDRO/88032 APOSTOL SAN PEDRO</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5141,72 +5035,70 @@
         <v>223500</v>
       </c>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" s="1" t="n">
+      <c r="K50" s="1" t="n">
         <v>45638</v>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>27/11/2024</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>26/11/2028</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>26/11/2028</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>YUNGAY</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>YUNGAY</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>AURA</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>022001</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>AURA</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>022001</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>86625 ANGELICA HARADA VASQUEZ/86625 ANGELICA HARADA VASQUEZ</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>UGEL YUNGAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
-        <is>
-          <t>86625 ANGELICA HARADA VASQUEZ/86625 ANGELICA HARADA VASQUEZ</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5251,74 +5143,72 @@
         <v>230305</v>
       </c>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>20/12/2024 - 07/03/2025</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>30/12/2024</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>20/12/2024 - 07/03/2025</t>
+          <t>29/12/2028</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>29/12/2028</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>YUNGAY</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>YUNGAY</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>TUMPA</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>022001</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>TUMPA</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>022001</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>86620 SANTA FE/86620 SANTA FE</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>UGEL YUNGAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
-        <is>
-          <t>86620 SANTA FE/86620 SANTA FE</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5363,72 +5253,70 @@
         <v>253500</v>
       </c>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" s="1" t="n">
+      <c r="K52" s="1" t="n">
         <v>45636</v>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>10/01/2025</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>09/01/2029</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>09/01/2029</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>CASTROVIRREYNA</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>AURAHUA</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>CASTROVIRREYNA</t>
+          <t>COCHAMARCA</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>AURAHUA</t>
+          <t>090403</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>COCHAMARCA</t>
+          <t>DRE HUANCAVELICA</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>090403</t>
+          <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>DRE HUANCAVELICA</t>
+          <t>ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>UGEL CASTROVIRREYNA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5473,72 +5361,70 @@
         <v>225500</v>
       </c>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" s="1" t="n">
+      <c r="K53" s="1" t="n">
         <v>45519</v>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>21/01/2025</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>20/01/2029</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>21/01/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>20/01/2029</t>
+          <t>LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>HUAROCHIRI</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>SANTA CRUZ DE COCACHACRA</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>HUAROCHIRI</t>
+          <t>CORCONA</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>SANTA CRUZ DE COCACHACRA</t>
+          <t>150727</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>CORCONA</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>150727</t>
+          <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>20811 REPUBLICA DE COLOMBIA/20811 REPUBLICA DE COLOMBIA/20811 REPUBLICA DE COLOMBIA</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>UGEL 15 HUAROCHIRÍ</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
-        <is>
-          <t>20811 REPUBLICA DE COLOMBIA/20811 REPUBLICA DE COLOMBIA/20811 REPUBLICA DE COLOMBIA</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5583,72 +5469,70 @@
         <v>223500</v>
       </c>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" s="1" t="n">
+      <c r="K54" s="1" t="n">
         <v>45678</v>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>04/05/2029</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>04/05/2029</t>
+          <t>LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>HUAROCHIRI</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>SAN JUAN DE TANTARANCHE</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>HUAROCHIRI</t>
+          <t>SAN JUAN DE TUNTARANCHE</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>SAN JUAN DE TANTARANCHE</t>
+          <t>150720</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>SAN JUAN DE TUNTARANCHE</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>150720</t>
+          <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>20653 SAN JUAN BAUTISTA PRECURSOR/20653 SAN JUAN BAUTISTA PRECURSOR/20653 SAN JUAN BAUTISTA PRECURSOR</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>UGEL 15 HUAROCHIRÍ</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
-        <is>
-          <t>20653 SAN JUAN BAUTISTA PRECURSOR/20653 SAN JUAN BAUTISTA PRECURSOR/20653 SAN JUAN BAUTISTA PRECURSOR</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5682,59 +5566,57 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>CURGOS</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>SANCHEZ CARRION</t>
+          <t>CURGOS</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>CURGOS</t>
+          <t>130904</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>CURGOS</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>130904</t>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>GRE LA LIBERTAD</t>
+          <t>80138 ABELARDO GAMARRA RONDO/80138 ABELARDO GAMARRA RONDO</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>UGEL SÁNCHEZ CARRIÓN</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
-        <is>
-          <t>80138 ABELARDO GAMARRA RONDO/80138 ABELARDO GAMARRA RONDO</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5779,72 +5661,70 @@
         <v>218472.63</v>
       </c>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" s="1" t="n">
+      <c r="K56" s="1" t="n">
         <v>45322</v>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>10/01/2025</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>09/01/2029</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>09/01/2029</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>PACASMAYO</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>PACASMAYO</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE LLOC</t>
+          <t>130701</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE LLOC</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>UGEL PACASMAYO</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>GRE LA LIBERTAD</t>
+          <t>80374 JOSE SEVILLA ESCAJADILLO</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>UGEL PACASMAYO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
-        <is>
-          <t>80374 JOSE SEVILLA ESCAJADILLO</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5878,16 +5758,24 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5897,40 +5785,30 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>200601</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>200601</t>
+          <t>UGEL SULLANA</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>JOSE MATIAS MANZANILLA</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>UGEL SULLANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>JOSE MATIAS MANZANILLA</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -5964,59 +5842,57 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>TALARA</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>LA BREA</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>TALARA</t>
+          <t>NEGRITOS</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
+          <t>200703</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
           <t>LA BREA</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>NEGRITOS</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>200703</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>DRE PIURA</t>
-        </is>
-      </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>UGEL TALARA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
-        <is>
-          <t>LA BREA</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6050,11 +5926,19 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>TUMBES</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -6064,45 +5948,35 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>TUMBES</t>
+          <t>SALAMANCA</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>TUMBES</t>
+          <t>240101</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>SALAMANCA</t>
+          <t>DRE TUMBES</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>240101</t>
+          <t>DRE TUMBES</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>DRE TUMBES</t>
+          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>DRE TUMBES</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
-        <is>
-          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6147,72 +6021,70 @@
         <v>144445.24</v>
       </c>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" s="1" t="n">
+      <c r="K60" s="1" t="n">
         <v>45344</v>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>HUANCABAMBA</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>HUARMACA</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>HUANCABAMBA</t>
+          <t>CUSE</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>HUARMACA</t>
+          <t>200304</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>CUSE</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>200304</t>
+          <t>UGEL HUARMACA</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14594 SAN JOSE/14594 SAN JOSE/14594 SAN JOSE</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>UGEL HUARMACA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
-        <is>
-          <t>14594 SAN JOSE/14594 SAN JOSE/14594 SAN JOSE</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6257,72 +6129,70 @@
         <v>163361.45</v>
       </c>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" s="1" t="n">
+      <c r="K61" s="1" t="n">
         <v>45593</v>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>LA ARENA</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>LAS MALVINAS</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>LA ARENA</t>
+          <t>200109</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>LAS MALVINAS</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>200109</t>
+          <t>UGEL LA UNIÓN</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>COLEGIO TECNICO DE APLICACION/COLEGIO TECNICO DE APLICACION</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>UGEL LA UNIÓN</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
-        <is>
-          <t>COLEGIO TECNICO DE APLICACION/COLEGIO TECNICO DE APLICACION</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6367,72 +6237,70 @@
         <v>151483.45</v>
       </c>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" s="1" t="n">
+      <c r="K62" s="1" t="n">
         <v>45604</v>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>MORROPON</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>BUENOS AIRES</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>MORROPON</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>BUENOS AIRES</t>
+          <t>200402</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>PUEBLO NUEVO</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>200402</t>
+          <t>UGEL MORROPÓN</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>UGEL MORROPÓN</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
-        <is>
-          <t>14641</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6477,29 +6345,37 @@
         <v>126461.5</v>
       </c>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" s="1" t="n">
+      <c r="K63" s="1" t="n">
         <v>45446</v>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6509,40 +6385,30 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>200601</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>200601</t>
+          <t>UGEL SULLANA</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14790 MARIA IGNACIA GARCIA DE GONZALES/14790 MARIA IGNACIA GARCIA</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>UGEL SULLANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
-        <is>
-          <t>14790 MARIA IGNACIA GARCIA DE GONZALES/14790 MARIA IGNACIA GARCIA</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6587,72 +6453,70 @@
         <v>122694.35</v>
       </c>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" s="1" t="n">
+      <c r="K64" s="1" t="n">
         <v>45447</v>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>IGNACIO ESCUDERO</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>SAN JOSE</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>IGNACIO ESCUDERO</t>
+          <t>200603</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>SAN JOSE</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>200603</t>
+          <t>UGEL SULLANA</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>20509/20509</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>UGEL SULLANA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
-        <is>
-          <t>20509/20509</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6697,72 +6561,70 @@
         <v>186381.43</v>
       </c>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" s="1" t="n">
+      <c r="K65" s="1" t="n">
         <v>45733</v>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>17/03/2025</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>16/03/2029</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>17/03/2025</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>16/03/2029</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>TAMBO GRANDE</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>MALINGAS</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>TAMBO GRANDE</t>
+          <t>200114</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>MALINGAS</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>200114</t>
+          <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14924 DANIEL ALCIDES CARRION/14924 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>UGEL TAMBOGRANDE</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
-        <is>
-          <t>14924 DANIEL ALCIDES CARRION/14924 DANIEL ALCIDES CARRION</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6796,59 +6658,57 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CURA MORI</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>ALMIRANTE GRAU</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>CURA MORI</t>
+          <t>200107</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>ALMIRANTE GRAU</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>200107</t>
+          <t>UGEL PIURA</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>CORONEL JOSE ANDRES RAZURI/CORONEL JOSE ANDRES RAZURI/CORONEL JOSE ANDRES RAZURI</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>UGEL PIURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
-        <is>
-          <t>CORONEL JOSE ANDRES RAZURI/CORONEL JOSE ANDRES RAZURI/CORONEL JOSE ANDRES RAZURI</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6882,16 +6742,24 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6901,40 +6769,30 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>200601</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>200601</t>
+          <t>UGEL SULLANA</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>15079/15079/15079</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>UGEL SULLANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
-        <is>
-          <t>15079/15079/15079</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -6979,29 +6837,37 @@
         <v>144607.5</v>
       </c>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" s="1" t="n">
+      <c r="K68" s="1" t="n">
         <v>45341</v>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>01/12/2028</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>01/12/2028</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Se consigna en el año 2026 la estimación de monto de acuerdo a la programación del mantemiento programado.</t>
+          <t>TALARA</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>PARIÑAS</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -7011,40 +6877,30 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>PARIÑAS</t>
+          <t>200701</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>TALARA</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>200701</t>
+          <t>UGEL TALARA</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>15508 DOMINGO SAVIO/15508 DOMINGO SAVIO/15508 DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>UGEL TALARA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
-        <is>
-          <t>15508 DOMINGO SAVIO/15508 DOMINGO SAVIO/15508 DOMINGO SAVIO</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -7078,59 +6934,57 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>200105</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>200105</t>
+          <t>UGEL PIURA</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>GENARO MARTINEZ SILVA/GENARO MARTINEZ SILVA/GENARO MARTINEZ SILVA</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>UGEL PIURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
-        <is>
-          <t>GENARO MARTINEZ SILVA/GENARO MARTINEZ SILVA/GENARO MARTINEZ SILVA</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -7164,59 +7018,57 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>PUEBLO NUEVO DE CATACAOS</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>200105</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>PUEBLO NUEVO DE CATACAOS</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>200105</t>
+          <t>UGEL PIURA</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>JOSE JACOBO CRUZ VILLEGAS/JOSE JACOBO CRUZ VILLEGAS</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>UGEL PIURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
-        <is>
-          <t>JOSE JACOBO CRUZ VILLEGAS/JOSE JACOBO CRUZ VILLEGAS</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -7250,59 +7102,57 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>200105</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>200105</t>
+          <t>UGEL PIURA</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>JOSE CAYETANO HEREDIA</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>UGEL PIURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
-        <is>
-          <t>JOSE CAYETANO HEREDIA</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -7336,16 +7186,24 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7355,40 +7213,30 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>200601</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>200601</t>
+          <t>UGEL SULLANA</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>15027 AMAUTA/15027 AMAUTA/15027 AMAUTA</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>UGEL SULLANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
-        <is>
-          <t>15027 AMAUTA/15027 AMAUTA/15027 AMAUTA</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -7422,16 +7270,24 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -7441,40 +7297,30 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>200601</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>200601</t>
+          <t>UGEL SULLANA</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>517</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>UGEL SULLANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -7508,59 +7354,57 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>TABLAZO SUR</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>LA UNION</t>
+          <t>200110</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>TABLAZO SUR</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>200110</t>
+          <t>UGEL LA UNIÓN</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>UGEL LA UNIÓN</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
-        <is>
-          <t>14064</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -7594,59 +7438,57 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CATACAOS</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>200105</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>CATACAOS</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>200105</t>
+          <t>UGEL PIURA</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>DRE PIURA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>UGEL PIURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
-        <is>
-          <t>MARIA AUXILIADORA</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -7680,59 +7522,57 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>YUNGAY</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>YUNGAY</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>LOMA</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>022001</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>LOMA</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>022001</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>86756</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>UGEL YUNGAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
-        <is>
-          <t>86756</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
@@ -7766,59 +7606,57 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>La institución educativa no se encuentra prevista en el PAM – 2026 de la ANIN, y se encuentra a cargo del mantenimiento por parte de la UGEL.</t>
+          <t>YUNGAY</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>YUNGAY</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>PATAPATA</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>022001</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>PATAPATA</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>022001</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>86657 JUAN CLAROS VERAZ/86657 JUAN CLAROS VERAZ/86657 JUAN CLAROS VERAZ</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>UGEL YUNGAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
-        <is>
-          <t>86657 JUAN CLAROS VERAZ/86657 JUAN CLAROS VERAZ/86657 JUAN CLAROS VERAZ</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
         <is>
           <t>ANIN</t>
         </is>
